--- a/Advance_template.xlsx
+++ b/Advance_template.xlsx
@@ -10,8 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap Partners Funded By CV" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap Partners" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workday Apvl" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1194,132 +1192,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>tc={25AE6CFB-3BD4-4A63-9930-09D2845C27C0}</author>
-    <author>tc={8E721154-832E-420A-8CEE-B6E783B7267E}</author>
-    <author>tc={EB75EDC9-39F9-417B-9105-5CFFF0242C79}</author>
-  </authors>
-  <commentList>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Includes 32 India fundings from escrow
-</t>
-      </text>
-    </comment>
-    <comment ref="D14" authorId="1" shapeId="0">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Includes 32 India fundings from escrow
-</t>
-      </text>
-    </comment>
-    <comment ref="D25" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Includes 32 india escro funding
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1666875</colOff>
-      <row>6</row>
-      <rowOff>103628</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Picture 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1333500" y="381000"/>
-          <a:ext cx="1666875" cy="1113278"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>7</col>
-      <colOff>276225</colOff>
-      <row>41</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>10</col>
-      <colOff>772424</colOff>
-      <row>46</row>
-      <rowOff>19175</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Picture 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="7439025" y="8181975"/>
-          <a:ext cx="6439799" cy="895475"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1587,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AM1100"/>
+  <dimension ref="A1:AM1100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.6328125" defaultRowHeight="13"/>
   <cols>
     <col width="7" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
@@ -1632,6 +1504,7 @@
     <col width="14.6328125" customWidth="1" style="1" min="40" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="14.5" customHeight="1">
       <c r="A2" s="12" t="n"/>
       <c r="B2" s="191" t="inlineStr">
@@ -46905,7 +46778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AM45"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10.6328125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -46915,13 +46788,10 @@
     <col width="12.90625" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="13" customFormat="1" customHeight="1" s="1">
       <c r="A2" s="20" t="n"/>
-      <c r="B2" s="34" t="inlineStr">
-        <is>
-          <t>This Month</t>
-        </is>
-      </c>
+      <c r="B2" s="34" t="n"/>
       <c r="C2" s="117" t="n"/>
       <c r="D2" s="34" t="n"/>
       <c r="E2" s="21" t="n"/>
@@ -46962,10 +46832,7 @@
     </row>
     <row r="3" customFormat="1" s="1">
       <c r="A3" s="12" t="n"/>
-      <c r="B3" s="17">
-        <f>'Combined Funding Request'!E6+4771277</f>
-        <v/>
-      </c>
+      <c r="B3" s="17" t="n"/>
       <c r="C3" s="112" t="n"/>
       <c r="D3" s="99" t="n"/>
       <c r="E3" s="127" t="n"/>
@@ -47039,11 +46906,7 @@
     </row>
     <row r="5" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A5" s="12" t="n"/>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>2024 TOTALS</t>
-        </is>
-      </c>
+      <c r="B5" s="18" t="n"/>
       <c r="C5" s="18" t="n"/>
       <c r="D5" s="29" t="n"/>
       <c r="E5" s="20" t="n"/>
@@ -47080,16 +46943,9 @@
     </row>
     <row r="6" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A6" s="12" t="n"/>
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="B6" s="36" t="n"/>
       <c r="C6" s="38" t="n"/>
-      <c r="D6" s="37">
-        <f>32637868+516891+22686191+18136556</f>
-        <v/>
-      </c>
+      <c r="D6" s="37" t="n"/>
       <c r="E6" s="20" t="n"/>
       <c r="F6" s="182" t="n"/>
       <c r="G6" s="169" t="n"/>
@@ -47125,16 +46981,9 @@
     </row>
     <row r="7" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A7" s="12" t="n"/>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 </t>
-        </is>
-      </c>
+      <c r="B7" s="36" t="n"/>
       <c r="C7" s="36" t="n"/>
-      <c r="D7" s="37">
-        <f>20068276+19832194+17050124</f>
-        <v/>
-      </c>
+      <c r="D7" s="37" t="n"/>
       <c r="E7" s="20" t="n"/>
       <c r="F7" s="53" t="n"/>
       <c r="G7" s="53" t="n"/>
@@ -47170,16 +47019,9 @@
     </row>
     <row r="8" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A8" s="12" t="n"/>
-      <c r="B8" s="36" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+      <c r="B8" s="36" t="n"/>
       <c r="C8" s="36" t="n"/>
-      <c r="D8" s="38">
-        <f>16158397+14364684+22952580</f>
-        <v/>
-      </c>
+      <c r="D8" s="38" t="n"/>
       <c r="E8" s="1" t="n"/>
       <c r="F8" s="53" t="n"/>
       <c r="G8" s="53" t="n"/>
@@ -47215,16 +47057,9 @@
     </row>
     <row r="9" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A9" s="12" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
-        <is>
-          <t>Q4 (running)</t>
-        </is>
-      </c>
+      <c r="B9" s="36" t="n"/>
       <c r="C9" s="36" t="n"/>
-      <c r="D9" s="38">
-        <f>B3+0</f>
-        <v/>
-      </c>
+      <c r="D9" s="38" t="n"/>
       <c r="E9" s="20" t="n"/>
       <c r="F9" s="53" t="n"/>
       <c r="G9" s="53" t="n"/>
@@ -47260,16 +47095,9 @@
     </row>
     <row r="10" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A10" s="12" t="n"/>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="B10" s="39" t="n"/>
       <c r="C10" s="39" t="n"/>
-      <c r="D10" s="40">
-        <f>SUM(D6:D9)</f>
-        <v/>
-      </c>
+      <c r="D10" s="40" t="n"/>
       <c r="E10" s="20" t="n"/>
       <c r="F10" s="53" t="n"/>
       <c r="G10" s="53" t="n"/>
@@ -47380,16 +47208,8 @@
     </row>
     <row r="13" ht="14" customFormat="1" customHeight="1" s="71">
       <c r="A13" s="12" t="n"/>
-      <c r="B13" s="147" t="inlineStr">
-        <is>
-          <t>2024 TOTALS</t>
-        </is>
-      </c>
-      <c r="C13" s="148" t="inlineStr">
-        <is>
-          <t>FNF Included in the above total</t>
-        </is>
-      </c>
+      <c r="B13" s="147" t="n"/>
+      <c r="C13" s="148" t="n"/>
       <c r="D13" s="149" t="n"/>
       <c r="E13" s="20" t="n"/>
       <c r="F13" s="53" t="n"/>
@@ -47426,17 +47246,9 @@
     </row>
     <row r="14" ht="14" customFormat="1" customHeight="1" s="71">
       <c r="A14" s="12" t="n"/>
-      <c r="B14" s="150" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C14" s="150" t="n">
-        <v>242</v>
-      </c>
-      <c r="D14" s="151" t="n">
-        <v>12219825.38</v>
-      </c>
+      <c r="B14" s="150" t="n"/>
+      <c r="C14" s="150" t="n"/>
+      <c r="D14" s="151" t="n"/>
       <c r="E14" s="20" t="n"/>
       <c r="F14" s="53" t="n"/>
       <c r="G14" s="53" t="n"/>
@@ -47472,17 +47284,9 @@
     </row>
     <row r="15" customFormat="1" s="71">
       <c r="A15" s="12" t="n"/>
-      <c r="B15" s="150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 </t>
-        </is>
-      </c>
-      <c r="C15" s="150" t="n">
-        <v>291</v>
-      </c>
-      <c r="D15" s="151" t="n">
-        <v>14889394.07</v>
-      </c>
+      <c r="B15" s="150" t="n"/>
+      <c r="C15" s="150" t="n"/>
+      <c r="D15" s="151" t="n"/>
       <c r="E15" s="20" t="n"/>
       <c r="F15" s="179" t="n"/>
       <c r="G15" s="175" t="n"/>
@@ -47518,30 +47322,12 @@
     </row>
     <row r="16" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A16" s="12" t="n"/>
-      <c r="B16" s="150" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="C16" s="150">
-        <f>118+197+153</f>
-        <v/>
-      </c>
-      <c r="D16" s="153">
-        <f>5672100.14+9491758+9121750</f>
-        <v/>
-      </c>
-      <c r="E16" s="152" t="inlineStr">
-        <is>
-          <t>This month</t>
-        </is>
-      </c>
+      <c r="B16" s="150" t="n"/>
+      <c r="C16" s="150" t="n"/>
+      <c r="D16" s="153" t="n"/>
+      <c r="E16" s="152" t="n"/>
       <c r="F16" s="1" t="n"/>
-      <c r="G16" s="152" t="inlineStr">
-        <is>
-          <t>This week</t>
-        </is>
-      </c>
+      <c r="G16" s="152" t="n"/>
       <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="175" t="n"/>
@@ -47574,34 +47360,13 @@
     </row>
     <row r="17" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A17" s="12" t="n"/>
-      <c r="B17" s="150" t="inlineStr">
-        <is>
-          <t>Q4 (running)</t>
-        </is>
-      </c>
-      <c r="C17" s="150">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="D17" s="153">
-        <f>E17</f>
-        <v/>
-      </c>
-      <c r="E17" s="99">
-        <f>2042859+G17</f>
-        <v/>
-      </c>
-      <c r="F17" s="156">
-        <f>H17+33</f>
-        <v/>
-      </c>
-      <c r="G17" s="99">
-        <f>SUM('Combined Funding Request'!U22:U26)</f>
-        <v/>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>5</v>
-      </c>
+      <c r="B17" s="150" t="n"/>
+      <c r="C17" s="150" t="n"/>
+      <c r="D17" s="153" t="n"/>
+      <c r="E17" s="99" t="n"/>
+      <c r="F17" s="156" t="n"/>
+      <c r="G17" s="99" t="n"/>
+      <c r="H17" s="12" t="n"/>
       <c r="I17" s="1" t="n"/>
       <c r="J17" s="1" t="n"/>
       <c r="K17" s="1" t="n"/>
@@ -47633,16 +47398,9 @@
     </row>
     <row r="18" ht="13" customFormat="1" customHeight="1" s="71">
       <c r="A18" s="12" t="n"/>
-      <c r="B18" s="154" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="B18" s="154" t="n"/>
       <c r="C18" s="154" t="n"/>
-      <c r="D18" s="155">
-        <f>SUM(D14:D17)</f>
-        <v/>
-      </c>
+      <c r="D18" s="155" t="n"/>
       <c r="E18" s="20" t="n"/>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="41" t="n"/>
@@ -47753,11 +47511,7 @@
     </row>
     <row r="21" customFormat="1" s="6">
       <c r="A21" s="12" t="n"/>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>2023 TOTALS</t>
-        </is>
-      </c>
+      <c r="B21" s="18" t="n"/>
       <c r="C21" s="18" t="n"/>
       <c r="D21" s="29" t="n"/>
       <c r="E21" s="20" t="n"/>
@@ -47795,15 +47549,9 @@
     </row>
     <row r="22" customFormat="1" s="6">
       <c r="A22" s="12" t="n"/>
-      <c r="B22" s="36" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="B22" s="36" t="n"/>
       <c r="C22" s="36" t="n"/>
-      <c r="D22" s="37" t="n">
-        <v>123361632</v>
-      </c>
+      <c r="D22" s="37" t="n"/>
       <c r="E22" s="20" t="n"/>
       <c r="F22" s="180" t="n"/>
       <c r="G22" s="53" t="n"/>
@@ -47839,15 +47587,9 @@
     </row>
     <row r="23" customFormat="1" s="6">
       <c r="A23" s="12" t="n"/>
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+      <c r="B23" s="36" t="n"/>
       <c r="C23" s="36" t="n"/>
-      <c r="D23" s="37" t="n">
-        <v>131895472</v>
-      </c>
+      <c r="D23" s="37" t="n"/>
       <c r="E23" s="20" t="n"/>
       <c r="F23" s="53" t="n"/>
       <c r="G23" s="53" t="n"/>
@@ -47883,15 +47625,9 @@
     </row>
     <row r="24" customFormat="1" s="6">
       <c r="A24" s="12" t="n"/>
-      <c r="B24" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 </t>
-        </is>
-      </c>
+      <c r="B24" s="36" t="n"/>
       <c r="C24" s="36" t="n"/>
-      <c r="D24" s="38" t="n">
-        <v>117941535</v>
-      </c>
+      <c r="D24" s="38" t="n"/>
       <c r="E24" s="1" t="n"/>
       <c r="F24" s="53" t="n"/>
       <c r="G24" s="53" t="n"/>
@@ -47927,16 +47663,9 @@
     </row>
     <row r="25" customFormat="1" s="6">
       <c r="A25" s="12" t="n"/>
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 </t>
-        </is>
-      </c>
+      <c r="B25" s="36" t="n"/>
       <c r="C25" s="36" t="n"/>
-      <c r="D25" s="38">
-        <f>88816025+6088095.71</f>
-        <v/>
-      </c>
+      <c r="D25" s="38" t="n"/>
       <c r="E25" s="1" t="n"/>
       <c r="F25" s="169" t="n"/>
       <c r="G25" s="53" t="n"/>
@@ -47972,16 +47701,9 @@
     </row>
     <row r="26" customFormat="1" s="6">
       <c r="A26" s="12" t="n"/>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="B26" s="39" t="n"/>
       <c r="C26" s="39" t="n"/>
-      <c r="D26" s="40">
-        <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
+      <c r="D26" s="40" t="n"/>
       <c r="E26" s="1" t="n"/>
       <c r="F26" s="169" t="n"/>
       <c r="G26" s="53" t="n"/>
@@ -48093,11 +47815,7 @@
     </row>
     <row r="29" customFormat="1" s="6">
       <c r="A29" s="12" t="n"/>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>2022 TOTALS</t>
-        </is>
-      </c>
+      <c r="B29" s="18" t="n"/>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="1" t="n"/>
       <c r="E29" s="1" t="n"/>
@@ -48135,15 +47853,9 @@
     </row>
     <row r="30" ht="13" customFormat="1" customHeight="1" s="6">
       <c r="A30" s="12" t="n"/>
-      <c r="B30" s="36" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="B30" s="36" t="n"/>
       <c r="C30" s="36" t="n"/>
-      <c r="D30" s="37" t="n">
-        <v>65299167</v>
-      </c>
+      <c r="D30" s="37" t="n"/>
       <c r="E30" s="1" t="n"/>
       <c r="F30" s="53" t="n"/>
       <c r="G30" s="53" t="n"/>
@@ -48179,15 +47891,9 @@
     </row>
     <row r="31" ht="13" customFormat="1" customHeight="1" s="6">
       <c r="A31" s="12" t="n"/>
-      <c r="B31" s="36" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+      <c r="B31" s="36" t="n"/>
       <c r="C31" s="36" t="n"/>
-      <c r="D31" s="37" t="n">
-        <v>100346718</v>
-      </c>
+      <c r="D31" s="37" t="n"/>
       <c r="E31" s="1" t="n"/>
       <c r="F31" s="53" t="n"/>
       <c r="G31" s="53" t="n"/>
@@ -48223,15 +47929,9 @@
     </row>
     <row r="32" ht="13" customFormat="1" customHeight="1" s="6">
       <c r="A32" s="12" t="n"/>
-      <c r="B32" s="36" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+      <c r="B32" s="36" t="n"/>
       <c r="C32" s="36" t="n"/>
-      <c r="D32" s="38" t="n">
-        <v>91894975</v>
-      </c>
+      <c r="D32" s="38" t="n"/>
       <c r="E32" s="1" t="n"/>
       <c r="F32" s="163" t="n"/>
       <c r="G32" s="53" t="n"/>
@@ -48267,15 +47967,9 @@
     </row>
     <row r="33" ht="13" customFormat="1" customHeight="1" s="6">
       <c r="A33" s="12" t="n"/>
-      <c r="B33" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 </t>
-        </is>
-      </c>
+      <c r="B33" s="36" t="n"/>
       <c r="C33" s="36" t="n"/>
-      <c r="D33" s="38" t="n">
-        <v>133525723</v>
-      </c>
+      <c r="D33" s="38" t="n"/>
       <c r="E33" s="1" t="n"/>
       <c r="F33" s="163" t="n"/>
       <c r="G33" s="53" t="n"/>
@@ -48311,16 +48005,9 @@
     </row>
     <row r="34" ht="13" customFormat="1" customHeight="1" s="6">
       <c r="A34" s="12" t="n"/>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="B34" s="39" t="n"/>
       <c r="C34" s="39" t="n"/>
-      <c r="D34" s="40">
-        <f>SUM(D30:D33)</f>
-        <v/>
-      </c>
+      <c r="D34" s="40" t="n"/>
       <c r="E34" s="1" t="n"/>
       <c r="F34" s="53" t="n"/>
       <c r="G34" s="53" t="n"/>
@@ -48418,11 +48105,7 @@
     </row>
     <row r="37" ht="13" customFormat="1" customHeight="1" s="1">
       <c r="A37" s="12" t="n"/>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>2021 TOTALS</t>
-        </is>
-      </c>
+      <c r="B37" s="18" t="n"/>
       <c r="C37" s="18" t="n"/>
       <c r="F37" s="53" t="n"/>
       <c r="G37" s="53" t="n"/>
@@ -48453,15 +48136,9 @@
     </row>
     <row r="38" ht="13" customFormat="1" customHeight="1" s="1">
       <c r="A38" s="12" t="n"/>
-      <c r="B38" s="36" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="B38" s="36" t="n"/>
       <c r="C38" s="36" t="n"/>
-      <c r="D38" s="37" t="n">
-        <v>31603965</v>
-      </c>
+      <c r="D38" s="37" t="n"/>
       <c r="F38" s="53" t="n"/>
       <c r="G38" s="53" t="n"/>
       <c r="H38" s="160" t="n"/>
@@ -48491,15 +48168,9 @@
     </row>
     <row r="39" ht="13" customFormat="1" customHeight="1" s="1">
       <c r="A39" s="12" t="n"/>
-      <c r="B39" s="36" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+      <c r="B39" s="36" t="n"/>
       <c r="C39" s="36" t="n"/>
-      <c r="D39" s="37" t="n">
-        <v>44539755</v>
-      </c>
+      <c r="D39" s="37" t="n"/>
       <c r="F39" s="53" t="n"/>
       <c r="G39" s="53" t="n"/>
       <c r="H39" s="160" t="n"/>
@@ -48529,15 +48200,9 @@
     </row>
     <row r="40" ht="13" customFormat="1" customHeight="1" s="1">
       <c r="A40" s="12" t="n"/>
-      <c r="B40" s="36" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+      <c r="B40" s="36" t="n"/>
       <c r="C40" s="36" t="n"/>
-      <c r="D40" s="38" t="n">
-        <v>51022808</v>
-      </c>
+      <c r="D40" s="38" t="n"/>
       <c r="F40" s="181" t="n"/>
       <c r="G40" s="53" t="n"/>
       <c r="H40" s="160" t="n"/>
@@ -48567,15 +48232,9 @@
     </row>
     <row r="41" ht="13" customFormat="1" customHeight="1" s="1">
       <c r="A41" s="12" t="n"/>
-      <c r="B41" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 </t>
-        </is>
-      </c>
+      <c r="B41" s="36" t="n"/>
       <c r="C41" s="36" t="n"/>
-      <c r="D41" s="38" t="n">
-        <v>63674947</v>
-      </c>
+      <c r="D41" s="38" t="n"/>
       <c r="H41" s="41" t="n"/>
       <c r="J41" s="53" t="n"/>
       <c r="K41" s="53" t="n"/>
@@ -48602,16 +48261,9 @@
     </row>
     <row r="42" ht="13" customFormat="1" customHeight="1" s="1">
       <c r="A42" s="12" t="n"/>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="B42" s="39" t="n"/>
       <c r="C42" s="39" t="n"/>
-      <c r="D42" s="40">
-        <f>SUM(D38:D41)</f>
-        <v/>
-      </c>
+      <c r="D42" s="40" t="n"/>
       <c r="H42" s="41" t="n"/>
       <c r="U42" s="126" t="n"/>
       <c r="AC42" s="4" t="n"/>
@@ -48683,7 +48335,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -48693,7 +48344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.453125" defaultRowHeight="13"/>
   <cols>
     <col width="11.453125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -48704,6 +48355,7 @@
     <col width="9.453125" customWidth="1" style="1" min="6" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="14.5" customHeight="1">
       <c r="B2" s="10" t="inlineStr">
         <is>
@@ -49039,7 +48691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.453125" defaultRowHeight="13"/>
   <cols>
     <col width="8.453125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -49051,6 +48703,7 @@
     <col width="9.453125" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="72.5" customHeight="1">
       <c r="B2" s="56" t="inlineStr">
         <is>
@@ -49269,1864 +48922,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M49"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col hidden="1" width="8.453125" customWidth="1" min="2" max="2"/>
-    <col hidden="1" width="20.453125" customWidth="1" min="3" max="3"/>
-    <col hidden="1" width="19.453125" customWidth="1" min="4" max="4"/>
-    <col width="34.453125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="25.1796875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="27.81640625" customWidth="1" min="7" max="7"/>
-    <col width="8" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="53.81640625" customWidth="1" min="9" max="9"/>
-    <col width="27.453125" customWidth="1" min="10" max="11"/>
-    <col width="17.453125" customWidth="1" min="12" max="12"/>
-    <col width="12.453125" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="208" t="n"/>
-      <c r="B1" s="77" t="n"/>
-      <c r="C1" s="77" t="n"/>
-      <c r="D1" s="77" t="n"/>
-      <c r="E1" s="77" t="n"/>
-      <c r="F1" s="77" t="n"/>
-      <c r="G1" s="77" t="n"/>
-      <c r="H1" s="77" t="n"/>
-      <c r="I1" s="77" t="n"/>
-      <c r="J1" s="77" t="n"/>
-      <c r="K1" s="77" t="n"/>
-      <c r="L1" s="77" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="208" t="n"/>
-      <c r="B2" s="78" t="inlineStr">
-        <is>
-          <t>Legacy Yardi Account</t>
-        </is>
-      </c>
-      <c r="C2" s="227" t="n"/>
-      <c r="D2" s="78" t="inlineStr">
-        <is>
-          <t>Legacy Yardi CC</t>
-        </is>
-      </c>
-      <c r="E2" s="79" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="F2" s="80" t="inlineStr">
-        <is>
-          <t>Spend Category</t>
-        </is>
-      </c>
-      <c r="G2" s="81" t="inlineStr">
-        <is>
-          <t>Cost Center</t>
-        </is>
-      </c>
-      <c r="H2" s="81" t="inlineStr">
-        <is>
-          <t>Loan</t>
-        </is>
-      </c>
-      <c r="I2" s="81" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="J2" s="81" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="K2" s="81" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="L2" s="81" t="inlineStr">
-        <is>
-          <t>Counterparty</t>
-        </is>
-      </c>
-      <c r="M2" s="81" t="inlineStr">
-        <is>
-          <t>Memo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="208" t="inlineStr">
-        <is>
-          <t>BANK ACCOUNT 5872</t>
-        </is>
-      </c>
-      <c r="B3" s="228" t="n"/>
-      <c r="C3" s="228" t="n"/>
-      <c r="D3" s="229" t="n"/>
-      <c r="E3" s="140" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F3" s="140" t="inlineStr">
-        <is>
-          <t>See Yard to Workday mapping examples below</t>
-        </is>
-      </c>
-      <c r="G3" s="196" t="inlineStr">
-        <is>
-          <t>Relevant construction cost centers:</t>
-        </is>
-      </c>
-      <c r="H3" s="140" t="inlineStr">
-        <is>
-          <t>Standard loan ID</t>
-        </is>
-      </c>
-      <c r="I3" s="83" t="inlineStr">
-        <is>
-          <t>.Required if line is for Principal</t>
-        </is>
-      </c>
-      <c r="J3" s="196" t="inlineStr">
-        <is>
-          <t>.Required if line is for Principal</t>
-        </is>
-      </c>
-      <c r="K3" s="196" t="inlineStr">
-        <is>
-          <t>.Always Required</t>
-        </is>
-      </c>
-      <c r="L3" s="196" t="n"/>
-      <c r="M3" s="196" t="n"/>
-    </row>
-    <row r="4" ht="24.5" customHeight="1">
-      <c r="D4" s="230" t="n"/>
-      <c r="E4" s="231" t="n"/>
-      <c r="F4" s="231" t="n"/>
-      <c r="G4" s="197" t="inlineStr">
-        <is>
-          <t>- 2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H4" s="231" t="n"/>
-      <c r="I4" s="85" t="inlineStr">
-        <is>
-          <t>.If loan starts with RB0 and company 184 or 185 (2021 or 2022 RTL1) = HFI - FVO</t>
-        </is>
-      </c>
-      <c r="J4" s="197" t="inlineStr">
-        <is>
-          <t>.Use code 'Advances'</t>
-        </is>
-      </c>
-      <c r="K4" s="197" t="inlineStr">
-        <is>
-          <t>.Use 'BPL - SAB' or 'BPL - Bridge'</t>
-        </is>
-      </c>
-      <c r="L4" s="197" t="n"/>
-      <c r="M4" s="197" t="n"/>
-    </row>
-    <row r="5">
-      <c r="D5" s="230" t="n"/>
-      <c r="E5" s="231" t="n"/>
-      <c r="F5" s="231" t="n"/>
-      <c r="G5" s="197" t="inlineStr">
-        <is>
-          <t>- 2240 SAB</t>
-        </is>
-      </c>
-      <c r="H5" s="231" t="n"/>
-      <c r="I5" s="85" t="inlineStr">
-        <is>
-          <t>.If loan starts with RB0 and not company 184 or 185 = HFS - FVO</t>
-        </is>
-      </c>
-      <c r="J5" s="197" t="n"/>
-      <c r="K5" s="197" t="n"/>
-      <c r="L5" s="197" t="n"/>
-      <c r="M5" s="197" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="232" t="n"/>
-      <c r="C6" s="232" t="n"/>
-      <c r="D6" s="233" t="n"/>
-      <c r="E6" s="234" t="n"/>
-      <c r="F6" s="234" t="n"/>
-      <c r="G6" s="197" t="inlineStr">
-        <is>
-          <t>- 4320 CoreVest Mortgage Banking</t>
-        </is>
-      </c>
-      <c r="H6" s="234" t="n"/>
-      <c r="I6" s="85" t="inlineStr">
-        <is>
-          <t>.If loan starts with RB1 = HFI - FVO</t>
-        </is>
-      </c>
-      <c r="J6" s="197" t="n"/>
-      <c r="K6" s="197" t="n"/>
-      <c r="L6" s="197" t="n"/>
-      <c r="M6" s="197" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="208" t="n"/>
-      <c r="B7" s="86" t="n"/>
-      <c r="C7" s="86" t="n"/>
-      <c r="D7" s="86" t="n"/>
-      <c r="E7" s="86" t="n"/>
-      <c r="F7" s="86" t="n"/>
-      <c r="G7" s="86" t="n"/>
-      <c r="H7" s="86" t="n"/>
-      <c r="I7" s="86" t="n"/>
-      <c r="J7" s="86" t="n"/>
-      <c r="K7" s="87" t="n"/>
-      <c r="L7" s="87" t="n"/>
-      <c r="M7" s="87" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="199" t="inlineStr">
-        <is>
-          <t>SAB - Principal - NLB rb0</t>
-        </is>
-      </c>
-      <c r="B8" s="88" t="inlineStr">
-        <is>
-          <t>2242-0000</t>
-        </is>
-      </c>
-      <c r="C8" s="88" t="inlineStr">
-        <is>
-          <t>Capital Partners Liability</t>
-        </is>
-      </c>
-      <c r="D8" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E8" s="88" t="inlineStr">
-        <is>
-          <t>180 Corevest Purchaser 2, LLC</t>
-        </is>
-      </c>
-      <c r="F8" s="88" t="inlineStr">
-        <is>
-          <t>FND - Principal</t>
-        </is>
-      </c>
-      <c r="G8" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H8" s="88" t="inlineStr">
-        <is>
-          <t>rb002304</t>
-        </is>
-      </c>
-      <c r="I8" s="88" t="inlineStr">
-        <is>
-          <t>HFS - FVO</t>
-        </is>
-      </c>
-      <c r="J8" s="88" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-      <c r="K8" s="88" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L8" s="88" t="n"/>
-      <c r="M8" s="88" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="230" t="n"/>
-      <c r="B9" s="89" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C9" s="89" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D9" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E9" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F9" s="89" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G9" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H9" s="89" t="inlineStr">
-        <is>
-          <t>rb002304</t>
-        </is>
-      </c>
-      <c r="I9" s="89" t="n"/>
-      <c r="J9" s="89" t="n"/>
-      <c r="K9" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L9" s="89" t="n"/>
-      <c r="M9" s="89" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="230" t="n"/>
-      <c r="B10" s="89" t="inlineStr">
-        <is>
-          <t>4321-0000</t>
-        </is>
-      </c>
-      <c r="C10" s="89" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D10" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E10" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F10" s="89" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G10" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H10" s="89" t="inlineStr">
-        <is>
-          <t>rb002304</t>
-        </is>
-      </c>
-      <c r="I10" s="89" t="n"/>
-      <c r="J10" s="89" t="n"/>
-      <c r="K10" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L10" s="89" t="n"/>
-      <c r="M10" s="89" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="208" t="n"/>
-      <c r="B11" s="86" t="n"/>
-      <c r="C11" s="86" t="n"/>
-      <c r="D11" s="86" t="n"/>
-      <c r="E11" s="86" t="n"/>
-      <c r="F11" s="86" t="n"/>
-      <c r="G11" s="86" t="n"/>
-      <c r="H11" s="86" t="n"/>
-      <c r="I11" s="86" t="n"/>
-      <c r="J11" s="86" t="n"/>
-      <c r="K11" s="87" t="n"/>
-      <c r="L11" s="87" t="n"/>
-      <c r="M11" s="87" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="199" t="inlineStr">
-        <is>
-          <t>SAB - Cap Partner Liability RB0</t>
-        </is>
-      </c>
-      <c r="B12" s="88" t="inlineStr">
-        <is>
-          <t>2242-0000</t>
-        </is>
-      </c>
-      <c r="C12" s="88" t="inlineStr">
-        <is>
-          <t>Capital Partners Liability</t>
-        </is>
-      </c>
-      <c r="D12" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E12" s="88" t="inlineStr">
-        <is>
-          <t>180 Corevest Purchaser 2, LLC</t>
-        </is>
-      </c>
-      <c r="F12" s="89" t="inlineStr">
-        <is>
-          <t>FND - Capital Partners Liability</t>
-        </is>
-      </c>
-      <c r="G12" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H12" s="89" t="inlineStr">
-        <is>
-          <t>rb042000</t>
-        </is>
-      </c>
-      <c r="I12" s="89" t="n"/>
-      <c r="J12" s="89" t="n"/>
-      <c r="K12" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L12" s="89" t="n"/>
-      <c r="M12" s="89" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="230" t="n"/>
-      <c r="B13" s="89" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C13" s="89" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D13" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E13" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F13" s="89" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G13" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H13" s="89" t="inlineStr">
-        <is>
-          <t>rb042000</t>
-        </is>
-      </c>
-      <c r="I13" s="89" t="n"/>
-      <c r="J13" s="89" t="n"/>
-      <c r="K13" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L13" s="89" t="n"/>
-      <c r="M13" s="89" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="230" t="n"/>
-      <c r="B14" s="89" t="inlineStr">
-        <is>
-          <t>4321-0000</t>
-        </is>
-      </c>
-      <c r="C14" s="89" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D14" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E14" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F14" s="89" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G14" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H14" s="89" t="inlineStr">
-        <is>
-          <t>rb042000</t>
-        </is>
-      </c>
-      <c r="I14" s="89" t="n"/>
-      <c r="J14" s="89" t="n"/>
-      <c r="K14" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L14" s="89" t="n"/>
-      <c r="M14" s="89" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="208" t="n"/>
-      <c r="B15" s="86" t="n"/>
-      <c r="C15" s="86" t="n"/>
-      <c r="D15" s="86" t="n"/>
-      <c r="E15" s="86" t="n"/>
-      <c r="F15" s="86" t="n"/>
-      <c r="G15" s="86" t="n"/>
-      <c r="H15" s="86" t="n"/>
-      <c r="I15" s="86" t="n"/>
-      <c r="J15" s="86" t="n"/>
-      <c r="K15" s="87" t="n"/>
-      <c r="L15" s="87" t="n"/>
-      <c r="M15" s="87" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="199" t="inlineStr">
-        <is>
-          <t>SAB - Cap Partner Liability RB1</t>
-        </is>
-      </c>
-      <c r="B16" s="88" t="inlineStr">
-        <is>
-          <t>2242-0000</t>
-        </is>
-      </c>
-      <c r="C16" s="88" t="inlineStr">
-        <is>
-          <t>Capital Partners Liability</t>
-        </is>
-      </c>
-      <c r="D16" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E16" s="89" t="inlineStr">
-        <is>
-          <t>181 Redwood BPL Holdings 2, Inc.</t>
-        </is>
-      </c>
-      <c r="F16" s="89" t="inlineStr">
-        <is>
-          <t>FND - Capital Partners Liability</t>
-        </is>
-      </c>
-      <c r="G16" s="174" t="inlineStr">
-        <is>
-          <t>4330 CoreVest Investments</t>
-        </is>
-      </c>
-      <c r="H16" s="89" t="inlineStr">
-        <is>
-          <t>rb142000</t>
-        </is>
-      </c>
-      <c r="I16" s="89" t="n"/>
-      <c r="J16" s="89" t="n"/>
-      <c r="K16" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L16" s="89" t="n"/>
-      <c r="M16" s="89" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="230" t="n"/>
-      <c r="B17" s="89" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C17" s="89" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D17" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E17" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F17" s="89" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G17" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H17" s="89" t="inlineStr">
-        <is>
-          <t>rb142000</t>
-        </is>
-      </c>
-      <c r="I17" s="89" t="n"/>
-      <c r="J17" s="89" t="n"/>
-      <c r="K17" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L17" s="89" t="n"/>
-      <c r="M17" s="89" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="230" t="n"/>
-      <c r="B18" s="89" t="inlineStr">
-        <is>
-          <t>4321-0000</t>
-        </is>
-      </c>
-      <c r="C18" s="89" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D18" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E18" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F18" s="89" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H18" s="89" t="inlineStr">
-        <is>
-          <t>rb142000</t>
-        </is>
-      </c>
-      <c r="I18" s="89" t="n"/>
-      <c r="J18" s="89" t="n"/>
-      <c r="K18" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L18" s="89" t="n"/>
-      <c r="M18" s="89" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="208" t="n"/>
-      <c r="B19" s="86" t="n"/>
-      <c r="C19" s="86" t="n"/>
-      <c r="D19" s="86" t="n"/>
-      <c r="E19" s="86" t="n"/>
-      <c r="F19" s="86" t="n"/>
-      <c r="G19" s="86" t="n"/>
-      <c r="H19" s="86" t="n"/>
-      <c r="I19" s="86" t="n"/>
-      <c r="J19" s="86" t="n"/>
-      <c r="K19" s="87" t="n"/>
-      <c r="L19" s="87" t="n"/>
-      <c r="M19" s="87" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="199" t="inlineStr">
-        <is>
-          <t>SAB - rb1 - NLB</t>
-        </is>
-      </c>
-      <c r="B20" s="89" t="inlineStr">
-        <is>
-          <t>1631-0000</t>
-        </is>
-      </c>
-      <c r="C20" s="88" t="inlineStr">
-        <is>
-          <t>Advances - Bridge</t>
-        </is>
-      </c>
-      <c r="D20" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E20" s="89" t="inlineStr">
-        <is>
-          <t>181 Redwood BPL Holdings 2, Inc.</t>
-        </is>
-      </c>
-      <c r="F20" s="89" t="inlineStr">
-        <is>
-          <t>FND - Principal</t>
-        </is>
-      </c>
-      <c r="G20" s="90" t="inlineStr">
-        <is>
-          <t>4330 CoreVest Investments</t>
-        </is>
-      </c>
-      <c r="H20" s="89" t="inlineStr">
-        <is>
-          <t>rb103044</t>
-        </is>
-      </c>
-      <c r="I20" s="89" t="inlineStr">
-        <is>
-          <t>HFI - FVO</t>
-        </is>
-      </c>
-      <c r="J20" s="89" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-      <c r="K20" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L20" s="89" t="n"/>
-      <c r="M20" s="89" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="230" t="n"/>
-      <c r="B21" s="89" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C21" s="89" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D21" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E21" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F21" s="89" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G21" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H21" s="89" t="inlineStr">
-        <is>
-          <t>rb103044</t>
-        </is>
-      </c>
-      <c r="I21" s="89" t="n"/>
-      <c r="J21" s="89" t="n"/>
-      <c r="K21" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L21" s="89" t="n"/>
-      <c r="M21" s="89" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="230" t="n"/>
-      <c r="B22" s="89" t="inlineStr">
-        <is>
-          <t>4621-0000</t>
-        </is>
-      </c>
-      <c r="C22" s="89" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D22" s="89" t="inlineStr">
-        <is>
-          <t>2241 Bridge Funding RB</t>
-        </is>
-      </c>
-      <c r="E22" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F22" s="89" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G22" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H22" s="89" t="inlineStr">
-        <is>
-          <t>rb103044</t>
-        </is>
-      </c>
-      <c r="I22" s="89" t="n"/>
-      <c r="J22" s="89" t="n"/>
-      <c r="K22" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L22" s="89" t="n"/>
-      <c r="M22" s="89" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="208" t="n"/>
-      <c r="B23" s="86" t="n"/>
-      <c r="C23" s="86" t="n"/>
-      <c r="D23" s="86" t="n"/>
-      <c r="E23" s="86" t="n"/>
-      <c r="F23" s="86" t="n"/>
-      <c r="G23" s="86" t="n"/>
-      <c r="H23" s="86" t="n"/>
-      <c r="I23" s="86" t="n"/>
-      <c r="J23" s="86" t="n"/>
-      <c r="K23" s="87" t="n"/>
-      <c r="L23" s="87" t="n"/>
-      <c r="M23" s="87" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="199" t="inlineStr">
-        <is>
-          <t>SAB - BPL2 - (CPP JV - Morgan Stanley &amp; Goldman &amp; WellsFargo)</t>
-        </is>
-      </c>
-      <c r="B24" s="89" t="inlineStr">
-        <is>
-          <t>1631-0000</t>
-        </is>
-      </c>
-      <c r="C24" s="88" t="inlineStr">
-        <is>
-          <t>Advances - Bridge</t>
-        </is>
-      </c>
-      <c r="D24" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E24" s="142" t="inlineStr">
-        <is>
-          <t>180 Corevest Purchaser 2, LLC</t>
-        </is>
-      </c>
-      <c r="F24" s="140" t="inlineStr">
-        <is>
-          <t>JV Fund Expenses</t>
-        </is>
-      </c>
-      <c r="G24" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H24" s="89" t="inlineStr">
-        <is>
-          <t>rb103044</t>
-        </is>
-      </c>
-      <c r="I24" s="89" t="n"/>
-      <c r="J24" s="187" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-      <c r="K24" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L24" s="89" t="inlineStr">
-        <is>
-          <t>CPP</t>
-        </is>
-      </c>
-      <c r="M24" s="89" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="230" t="n"/>
-      <c r="B25" s="89" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C25" s="89" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D25" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E25" s="145" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F25" s="146" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G25" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H25" s="89" t="inlineStr">
-        <is>
-          <t>rb103044</t>
-        </is>
-      </c>
-      <c r="I25" s="89" t="n"/>
-      <c r="J25" s="89" t="n"/>
-      <c r="K25" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L25" s="89" t="inlineStr">
-        <is>
-          <t>CPP</t>
-        </is>
-      </c>
-      <c r="M25" s="146" t="inlineStr">
-        <is>
-          <t>Appraisal Fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="230" t="n"/>
-      <c r="B26" s="89" t="inlineStr">
-        <is>
-          <t>4621-0000</t>
-        </is>
-      </c>
-      <c r="C26" s="89" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D26" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E26" s="145" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F26" s="146" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G26" s="89" t="inlineStr">
-        <is>
-          <t>2240 SAB</t>
-        </is>
-      </c>
-      <c r="H26" s="89" t="inlineStr">
-        <is>
-          <t>rb103044</t>
-        </is>
-      </c>
-      <c r="I26" s="89" t="n"/>
-      <c r="J26" s="89" t="n"/>
-      <c r="K26" s="89" t="inlineStr">
-        <is>
-          <t>BPL - SAB</t>
-        </is>
-      </c>
-      <c r="L26" s="89" t="inlineStr">
-        <is>
-          <t>CPP</t>
-        </is>
-      </c>
-      <c r="M26" s="146" t="inlineStr">
-        <is>
-          <t>Lender Fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="208" t="n"/>
-      <c r="B27" s="86" t="n"/>
-      <c r="C27" s="86" t="n"/>
-      <c r="D27" s="86" t="n"/>
-      <c r="E27" s="86" t="n"/>
-      <c r="F27" s="86" t="n"/>
-      <c r="G27" s="86" t="n"/>
-      <c r="H27" s="86" t="n"/>
-      <c r="I27" s="86" t="n"/>
-      <c r="J27" s="86" t="n"/>
-      <c r="K27" s="87" t="n"/>
-      <c r="L27" s="87" t="n"/>
-      <c r="M27" s="87" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="199" t="inlineStr">
-        <is>
-          <t>Bridge - BPL2 - LG</t>
-        </is>
-      </c>
-      <c r="B28" s="89" t="inlineStr">
-        <is>
-          <t>1631-0000</t>
-        </is>
-      </c>
-      <c r="C28" s="88" t="inlineStr">
-        <is>
-          <t>Advances - Bridge</t>
-        </is>
-      </c>
-      <c r="D28" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E28" s="89" t="inlineStr">
-        <is>
-          <t>181 Redwood BPL Holdings 2, Inc.</t>
-        </is>
-      </c>
-      <c r="F28" s="89" t="inlineStr">
-        <is>
-          <t>FND - Principal</t>
-        </is>
-      </c>
-      <c r="G28" s="90" t="inlineStr">
-        <is>
-          <t>4330 CoreVest Investments</t>
-        </is>
-      </c>
-      <c r="H28" s="90" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I28" s="89" t="inlineStr">
-        <is>
-          <t>HFI - FVO</t>
-        </is>
-      </c>
-      <c r="J28" s="89" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-      <c r="K28" s="89" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L28" s="89" t="n"/>
-      <c r="M28" s="89" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="230" t="n"/>
-      <c r="B29" s="89" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C29" s="89" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D29" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E29" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F29" s="89" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G29" s="90" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H29" s="90" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I29" s="89" t="n"/>
-      <c r="J29" s="89" t="n"/>
-      <c r="K29" s="89" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L29" s="89" t="n"/>
-      <c r="M29" s="89" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="230" t="n"/>
-      <c r="B30" s="89" t="inlineStr">
-        <is>
-          <t>4621-0000</t>
-        </is>
-      </c>
-      <c r="C30" s="89" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D30" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E30" s="89" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F30" s="89" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G30" s="90" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H30" s="90" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I30" s="89" t="n"/>
-      <c r="J30" s="89" t="n"/>
-      <c r="K30" s="89" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L30" s="89" t="n"/>
-      <c r="M30" s="89" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="208" t="n"/>
-      <c r="B31" s="86" t="n"/>
-      <c r="C31" s="86" t="n"/>
-      <c r="D31" s="86" t="n"/>
-      <c r="E31" s="86" t="n"/>
-      <c r="F31" s="86" t="n"/>
-      <c r="G31" s="86" t="n"/>
-      <c r="H31" s="86" t="n"/>
-      <c r="I31" s="86" t="n"/>
-      <c r="J31" s="86" t="n"/>
-      <c r="K31" s="87" t="n"/>
-      <c r="L31" s="87" t="n"/>
-      <c r="M31" s="87" t="n"/>
-    </row>
-    <row r="32" customFormat="1" s="144">
-      <c r="A32" s="204" t="inlineStr">
-        <is>
-          <t>Bridge - BPL2 - LG (JV-Churchill Warehouse line)</t>
-        </is>
-      </c>
-      <c r="B32" s="141" t="inlineStr">
-        <is>
-          <t>1631-0000</t>
-        </is>
-      </c>
-      <c r="C32" s="142" t="inlineStr">
-        <is>
-          <t>Advances - Bridge</t>
-        </is>
-      </c>
-      <c r="D32" s="141" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E32" s="142" t="inlineStr">
-        <is>
-          <t>180 Corevest Purchaser 2, LLC</t>
-        </is>
-      </c>
-      <c r="F32" s="140" t="inlineStr">
-        <is>
-          <t>JV Fund Expenses</t>
-        </is>
-      </c>
-      <c r="G32" s="143" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H32" s="143" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I32" s="141" t="n"/>
-      <c r="J32" s="187" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-      <c r="K32" s="141" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L32" s="89" t="inlineStr">
-        <is>
-          <t>Oaktree</t>
-        </is>
-      </c>
-      <c r="M32" s="89" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="1" s="144">
-      <c r="A33" s="230" t="n"/>
-      <c r="B33" s="141" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C33" s="141" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D33" s="141" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E33" s="141" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F33" s="146" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G33" s="143" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H33" s="143" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I33" s="141" t="n"/>
-      <c r="J33" s="141" t="n"/>
-      <c r="K33" s="141" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L33" s="89" t="inlineStr">
-        <is>
-          <t>Oaktree</t>
-        </is>
-      </c>
-      <c r="M33" s="146" t="inlineStr">
-        <is>
-          <t>Appraisal Fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="1" s="144">
-      <c r="A34" s="230" t="n"/>
-      <c r="B34" s="141" t="inlineStr">
-        <is>
-          <t>4621-0000</t>
-        </is>
-      </c>
-      <c r="C34" s="141" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D34" s="141" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E34" s="141" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F34" s="146" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G34" s="143" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H34" s="143" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I34" s="141" t="n"/>
-      <c r="J34" s="141" t="n"/>
-      <c r="K34" s="141" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L34" s="89" t="inlineStr">
-        <is>
-          <t>Oaktree</t>
-        </is>
-      </c>
-      <c r="M34" s="146" t="inlineStr">
-        <is>
-          <t>Lender Fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customFormat="1" customHeight="1" s="136">
-      <c r="A35" s="137" t="n"/>
-      <c r="B35" s="138" t="n"/>
-      <c r="C35" s="138" t="n"/>
-      <c r="D35" s="138" t="n"/>
-      <c r="E35" s="138" t="n"/>
-      <c r="F35" s="138" t="n"/>
-      <c r="G35" s="138" t="n"/>
-      <c r="H35" s="138" t="n"/>
-      <c r="I35" s="138" t="n"/>
-      <c r="J35" s="86" t="n"/>
-      <c r="K35" s="139" t="n"/>
-      <c r="L35" s="139" t="n"/>
-      <c r="M35" s="139" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="199" t="inlineStr">
-        <is>
-          <t>Bridge - BPL2 - LG (CPP JV - Morgan Stanley &amp; Goldman &amp; WellsFargo)</t>
-        </is>
-      </c>
-      <c r="B36" s="89" t="inlineStr">
-        <is>
-          <t>1631-0000</t>
-        </is>
-      </c>
-      <c r="C36" s="88" t="inlineStr">
-        <is>
-          <t>Advances - Bridge</t>
-        </is>
-      </c>
-      <c r="D36" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E36" s="142" t="inlineStr">
-        <is>
-          <t>180 Corevest Purchaser 2, LLC</t>
-        </is>
-      </c>
-      <c r="F36" s="140" t="inlineStr">
-        <is>
-          <t>JV Fund Expenses</t>
-        </is>
-      </c>
-      <c r="G36" s="90" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H36" s="90" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I36" s="89" t="n"/>
-      <c r="J36" s="187" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-      <c r="K36" s="89" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L36" s="89" t="inlineStr">
-        <is>
-          <t>CPP</t>
-        </is>
-      </c>
-      <c r="M36" s="89" t="inlineStr">
-        <is>
-          <t>Advances</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="230" t="n"/>
-      <c r="B37" s="89" t="inlineStr">
-        <is>
-          <t>2188-0000</t>
-        </is>
-      </c>
-      <c r="C37" s="89" t="inlineStr">
-        <is>
-          <t>Accrued - Appraisal Fee</t>
-        </is>
-      </c>
-      <c r="D37" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E37" s="145" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F37" s="146" t="inlineStr">
-        <is>
-          <t>FND - Accrued Appraisal Fees</t>
-        </is>
-      </c>
-      <c r="G37" s="90" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H37" s="90" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I37" s="89" t="n"/>
-      <c r="J37" s="89" t="n"/>
-      <c r="K37" s="89" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L37" s="89" t="inlineStr">
-        <is>
-          <t>CPP</t>
-        </is>
-      </c>
-      <c r="M37" s="146" t="inlineStr">
-        <is>
-          <t>Appraisal Fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="230" t="n"/>
-      <c r="B38" s="89" t="inlineStr">
-        <is>
-          <t>4621-0000</t>
-        </is>
-      </c>
-      <c r="C38" s="89" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D38" s="89" t="inlineStr">
-        <is>
-          <t>2201 Bridge Funding</t>
-        </is>
-      </c>
-      <c r="E38" s="145" t="inlineStr">
-        <is>
-          <t>187 CoreVest American Finance Lender LLC</t>
-        </is>
-      </c>
-      <c r="F38" s="146" t="inlineStr">
-        <is>
-          <t>FND - Lender Fees</t>
-        </is>
-      </c>
-      <c r="G38" s="90" t="inlineStr">
-        <is>
-          <t>2200 Bridge</t>
-        </is>
-      </c>
-      <c r="H38" s="90" t="n">
-        <v>44659004</v>
-      </c>
-      <c r="I38" s="89" t="n"/>
-      <c r="J38" s="89" t="n"/>
-      <c r="K38" s="89" t="inlineStr">
-        <is>
-          <t>BPL - Bridge</t>
-        </is>
-      </c>
-      <c r="L38" s="89" t="inlineStr">
-        <is>
-          <t>CPP</t>
-        </is>
-      </c>
-      <c r="M38" s="146" t="inlineStr">
-        <is>
-          <t>Lender Fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="208" t="n"/>
-      <c r="B39" s="86" t="n"/>
-      <c r="C39" s="86" t="n"/>
-      <c r="D39" s="86" t="n"/>
-      <c r="E39" s="86" t="n"/>
-      <c r="F39" s="86" t="n"/>
-      <c r="G39" s="86" t="n"/>
-      <c r="H39" s="86" t="n"/>
-      <c r="I39" s="86" t="n"/>
-      <c r="J39" s="86" t="n"/>
-      <c r="K39" s="87" t="n"/>
-      <c r="L39" s="87" t="n"/>
-      <c r="M39" s="87" t="n"/>
-    </row>
-    <row r="40">
-      <c r="C40" s="91" t="n"/>
-      <c r="D40" s="91" t="n"/>
-      <c r="E40" s="92" t="n"/>
-      <c r="F40" s="93" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="94" t="inlineStr">
-        <is>
-          <t>For the amounts we received from Statebridge, please change FND – Principal to FND - Escrow Deposit Liability and then please remove the HFI – FVO and Advances.</t>
-        </is>
-      </c>
-      <c r="C41" s="91" t="n"/>
-      <c r="D41" s="91" t="n"/>
-    </row>
-    <row r="42">
-      <c r="C42" s="91" t="n"/>
-      <c r="D42" s="91" t="n"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Processing invoices</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" s="91" t="n"/>
-      <c r="D43" s="91" t="n"/>
-      <c r="E43" s="92" t="n"/>
-      <c r="F43" s="93" t="n"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Asset id</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="91" t="n"/>
-      <c r="D44" s="91" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="93" t="n"/>
-      <c r="G44" s="235" t="inlineStr">
-        <is>
-          <t>Asset Address</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" s="91" t="n"/>
-      <c r="D45" s="91" t="n"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Dollar Amount approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Warehouse Line</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Deal Record Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Collecting fee from borrower</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" s="91" t="n"/>
-      <c r="D49" s="91" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="H3:H6"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A36:A38"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="I7:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="8.81640625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="44.453125" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="13.453125" customWidth="1" min="11" max="11"/>
-    <col width="17.453125" bestFit="1" customWidth="1" min="12" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="7">
-      <c r="I7" s="111" t="inlineStr">
-        <is>
-          <t>servicer #</t>
-        </is>
-      </c>
-      <c r="J7" s="111" t="n"/>
-      <c r="K7" s="111" t="inlineStr">
-        <is>
-          <t>next due date</t>
-        </is>
-      </c>
-      <c r="L7" s="111" t="inlineStr">
-        <is>
-          <t>IR remaining</t>
-        </is>
-      </c>
-      <c r="M7" s="111" t="inlineStr">
-        <is>
-          <t>IR payment amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1">
-      <c r="I8" s="109" t="n">
-        <v>38138001</v>
-      </c>
-      <c r="J8" s="110" t="inlineStr">
-        <is>
-          <t>Pebble Bridges</t>
-        </is>
-      </c>
-      <c r="K8" s="113" t="n">
-        <v>45361</v>
-      </c>
-      <c r="L8" s="236" t="n">
-        <v>436332.23</v>
-      </c>
-      <c r="M8" s="236" t="n">
-        <v>10343.43</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="I9" s="109" t="n">
-        <v>670399</v>
-      </c>
-      <c r="J9" s="110" t="inlineStr">
-        <is>
-          <t>Bevia Apartments</t>
-        </is>
-      </c>
-      <c r="K9" s="113" t="n">
-        <v>45361</v>
-      </c>
-      <c r="L9" s="236" t="n">
-        <v>377191.77</v>
-      </c>
-      <c r="M9" s="236" t="n">
-        <v>53429.02</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="I10" s="109" t="n">
-        <v>655259</v>
-      </c>
-      <c r="J10" s="110" t="inlineStr">
-        <is>
-          <t>Emerson Olde Town Townhomes</t>
-        </is>
-      </c>
-      <c r="K10" s="113" t="n">
-        <v>45361</v>
-      </c>
-      <c r="L10" s="236" t="n">
-        <v>439839.66</v>
-      </c>
-      <c r="M10" s="236" t="n">
-        <v>64052.63</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="I11" s="109" t="n">
-        <v>638276</v>
-      </c>
-      <c r="J11" s="110" t="inlineStr">
-        <is>
-          <t>Legacy at McKinney</t>
-        </is>
-      </c>
-      <c r="K11" s="113" t="n">
-        <v>45361</v>
-      </c>
-      <c r="L11" s="236" t="n">
-        <v>370820.09</v>
-      </c>
-      <c r="M11" s="236" t="n">
-        <v>160321.98</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="I12" s="109" t="n">
-        <v>599251</v>
-      </c>
-      <c r="J12" s="110" t="inlineStr">
-        <is>
-          <t>Viking Mill</t>
-        </is>
-      </c>
-      <c r="K12" s="113" t="n">
-        <v>45361</v>
-      </c>
-      <c r="L12" s="236" t="n">
-        <v>5018456.18</v>
-      </c>
-      <c r="M12" s="236" t="n">
-        <v>83917.88</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="I13" s="109" t="n">
-        <v>635332</v>
-      </c>
-      <c r="J13" s="110" t="inlineStr">
-        <is>
-          <t>Cassa Nashville</t>
-        </is>
-      </c>
-      <c r="K13" s="113" t="n">
-        <v>45361</v>
-      </c>
-      <c r="L13" s="236" t="n">
-        <v>973979.11</v>
-      </c>
-      <c r="M13" s="236" t="n">
-        <v>152247.53</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>